--- a/ReportsAndDocuments/presentation Qs.xlsx
+++ b/ReportsAndDocuments/presentation Qs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev1\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F479F4F-F3FF-444A-BD35-C23C4F62C6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D4598B-021B-434B-9B12-388BA52C1234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>product category:added</t>
+  </si>
+  <si>
+    <t>fault:no admin pannel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error msg </t>
+  </si>
+  <si>
+    <t>appear on modal</t>
   </si>
 </sst>
 </file>
@@ -348,12 +357,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/presentation Qs.xlsx
+++ b/ReportsAndDocuments/presentation Qs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev1\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D4598B-021B-434B-9B12-388BA52C1234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4F79BC-47D7-466E-808E-E918EB7F8FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t>product category:added</t>
   </si>
@@ -40,6 +40,87 @@
   </si>
   <si>
     <t>appear on modal</t>
+  </si>
+  <si>
+    <t>Tomatoes</t>
+  </si>
+  <si>
+    <t>Vegetables</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>Onions</t>
+  </si>
+  <si>
+    <t>Potatoes</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Eggs</t>
+  </si>
+  <si>
+    <t>dozen</t>
+  </si>
+  <si>
+    <t>Romaine</t>
+  </si>
+  <si>
+    <t>Raspberry</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Unsplash</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1626597825713-2cf6ad237229?crop=entropy&amp;cs=tinysrgb&amp;fit=max&amp;fm=jpg&amp;ixid=M3w5MTQwODN8MHwxfHNlYXJjaHwyfHxSYXNwYmVycnl8ZW58MHx8fHwxNzc1MTcyODg4fDA&amp;ixlib=rb-4.1.0&amp;q=80&amp;w=200</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1626597825713-2cf6ad237229?crop=entropy&amp;cs=tinysrgb&amp;fit=max&amp;fm=jpg&amp;ixid=M3w5MTQwODN8MHwxfHNlYXJjaHwyfHxSYXNwYmVycnl8ZW58MHx8fHwxNzc1MTcyODg4fDA&amp;ixlib=rb-4.1.0&amp;q=80&amp;w=400</t>
+  </si>
+  <si>
+    <t>Moon Moons</t>
+  </si>
+  <si>
+    <t>https://unsplash.com/@moonmoons_days</t>
+  </si>
+  <si>
+    <t>blueberry</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1594002348772-bc0cb57ade8b?crop=entropy&amp;cs=tinysrgb&amp;fit=max&amp;fm=jpg&amp;ixid=M3w5MTQwODN8MHwxfHNlYXJjaHwxfHxibHVlYmVycnl8ZW58MHx8fHwxNzc1MTczMDc2fDA&amp;ixlib=rb-4.1.0&amp;q=80&amp;w=200</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1594002348772-bc0cb57ade8b?crop=entropy&amp;cs=tinysrgb&amp;fit=max&amp;fm=jpg&amp;ixid=M3w5MTQwODN8MHwxfHNlYXJjaHwxfHxibHVlYmVycnl8ZW58MHx8fHwxNzc1MTczMDc2fDA&amp;ixlib=rb-4.1.0&amp;q=80&amp;w=400</t>
+  </si>
+  <si>
+    <t>Melissa Belanger</t>
+  </si>
+  <si>
+    <t>https://unsplash.com/@melissabelanger</t>
+  </si>
+  <si>
+    <t>product image added</t>
+  </si>
+  <si>
+    <t>change dropdown menu with modern menu options</t>
   </si>
 </sst>
 </file>
@@ -55,12 +136,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -75,8 +162,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,25 +445,296 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="7" max="7" width="37" customWidth="1"/>
+    <col min="8" max="8" width="74.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/presentation Qs.xlsx
+++ b/ReportsAndDocuments/presentation Qs.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev1\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4F79BC-47D7-466E-808E-E918EB7F8FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97794B54-8DEF-40A0-A41B-84BB43D930C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="83">
   <si>
     <t>product category:added</t>
   </si>
@@ -121,13 +122,169 @@
   </si>
   <si>
     <t>change dropdown menu with modern menu options</t>
+  </si>
+  <si>
+    <t>Change Area</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Forecast Model</t>
+  </si>
+  <si>
+    <t>The SSA model provides more accurate, data‑driven, and scalable demand forecasts by analyzing historical time‑series data, enabling better production planning and dispatch decisions.</t>
+  </si>
+  <si>
+    <t>Forecasting Integration (New Addition)</t>
+  </si>
+  <si>
+    <t>ML‑based demand forecasting was fully embedded into the operational workflow and used as a core input for vendor recommendations.</t>
+  </si>
+  <si>
+    <t>Integrating forecasting directly into decision support improved system intelligence and ensured that recommendations were driven by future demand rather than static historical data.</t>
+  </si>
+  <si>
+    <t>Dashboard Architecture</t>
+  </si>
+  <si>
+    <t>The dashboard was upgraded from a static UI design to a fully dynamic, API‑driven architecture supporting real‑time data updates.</t>
+  </si>
+  <si>
+    <t>This change improved system responsiveness and enabled real‑time visibility of inventory, requests, forecasts, and recommendations, enhancing user decision‑making.</t>
+  </si>
+  <si>
+    <t>Authentication and Security</t>
+  </si>
+  <si>
+    <t>Role‑based authentication was implemented using ASP.NET Identity with JWT‑based authorization.</t>
+  </si>
+  <si>
+    <t>Secure role separation was required to protect sensitive data and enforce access control between farmer and vendor functionalities.</t>
+  </si>
+  <si>
+    <t>Recommendation Logic</t>
+  </si>
+  <si>
+    <t>The original optimization‑based approach was simplified into a weighted scoring‑based recommendation system.</t>
+  </si>
+  <si>
+    <t>The scoring approach improved interpretability and usability, making recommendation logic easier for non‑technical agricultural users to understand and trust.</t>
+  </si>
+  <si>
+    <t>Relationship Tracking Enhancement</t>
+  </si>
+  <si>
+    <t>A new relationship‑tracking entity was introduced to record historical farmer–vendor interactions and compute a relationship score.</t>
+  </si>
+  <si>
+    <t>Including relationship history improved recommendation accuracy by accounting for prior collaboration performance and trust.</t>
+  </si>
+  <si>
+    <t>Location Feature</t>
+  </si>
+  <si>
+    <t>Latitude and longitude fields were added to user profiles to support geospatial calculations.</t>
+  </si>
+  <si>
+    <t>Geolocation data is required to compute distances between farmers and vendors, which is essential for distance‑based ranking and logistics optimization.</t>
+  </si>
+  <si>
+    <t>Data Generation Strategy</t>
+  </si>
+  <si>
+    <t>The initial simulated dataset approach was enhanced to include multi‑period historical demand, inventory, and dispatch data.</t>
+  </si>
+  <si>
+    <t>More realistic historical data was necessary to support reliable machine learning forecasting and to reflect real‑world agricultural scenarios.</t>
+  </si>
+  <si>
+    <t>User Experience Improvements</t>
+  </si>
+  <si>
+    <t>Searchable dropdowns, improved navigation through a shared sidebar layout, and improved input validation were introduced.</t>
+  </si>
+  <si>
+    <t>These changes significantly improved usability, reduced user errors, and enhanced overall interaction efficiency for both farmer and vendor roles.</t>
+  </si>
+  <si>
+    <t>Chat Module</t>
+  </si>
+  <si>
+    <t>A real‑time communication module was added using SignalR.</t>
+  </si>
+  <si>
+    <t>Real‑time messaging was required to support timely coordination, negotiations, and clarification during dispatch and fulfillment processes.</t>
+  </si>
+  <si>
+    <t>The initially proposed simple logic‑based demand estimation approach and Moving Average algorithm was replaced with a machine learning‑based forecasting model using ML.NET Singular Spectrum Analysis (SSA).</t>
+  </si>
+  <si>
+    <t>The initially proposed simple logic-based demand estimation approach and Moving Average algorithm was replaced with a machine learning-based forecasting model using ML.NET Singular Spectrum Analysis (SSA).</t>
+  </si>
+  <si>
+    <t>The SSA model provides more accurate, data-driven, and scalable demand forecasts by analyzing historical time-series data, enabling better production planning and dispatch decisions.</t>
+  </si>
+  <si>
+    <t>ML-based demand forecasting was fully embedded into the operational workflow and used as a core input for vendor recommendations.</t>
+  </si>
+  <si>
+    <t>The dashboard was upgraded from a static UI design to a fully dynamic, API-driven architecture supporting real-time data updates.</t>
+  </si>
+  <si>
+    <t>This change improved system responsiveness and enabled real-time visibility of inventory, requests, forecasts, and recommendations, enhancing user decision-making.</t>
+  </si>
+  <si>
+    <t>Role-based authentication was implemented using ASP.NET Identity with JWT-based authorization.</t>
+  </si>
+  <si>
+    <t>The original optimization-based approach was simplified into a weighted scoring-based recommendation system.</t>
+  </si>
+  <si>
+    <t>The scoring approach improved interpretability and usability, making recommendation logic easier for non-technical agricultural users to understand and trust.</t>
+  </si>
+  <si>
+    <t>A new relationship-tracking entity was introduced to record historical farmer–vendor interactions and compute a relationship score.</t>
+  </si>
+  <si>
+    <t>Geolocation data is required to compute distances between farmers and vendors, which is essential for distance-based ranking and logistics optimization.</t>
+  </si>
+  <si>
+    <t>The initial simulated dataset approach was enhanced to include multi-period historical demand, inventory, and dispatch data.</t>
+  </si>
+  <si>
+    <t>More realistic historical data was necessary to support reliable machine learning forecasting and to reflect real-world agricultural scenarios.</t>
+  </si>
+  <si>
+    <t>Searchable dropdowns, improved navigation through a shared sidebar layout, hover-based details, and enhanced input validation were introduced.</t>
+  </si>
+  <si>
+    <t>A real-time communication module was added using SignalR.</t>
+  </si>
+  <si>
+    <t>Real-time messaging was required to support timely coordination, negotiations, and clarification during dispatch and fulfillment processes.</t>
+  </si>
+  <si>
+    <t>Image Integration (Unsplash API – New Addition)</t>
+  </si>
+  <si>
+    <t>Product images were integrated using the Unsplash API to dynamically display images in dropdowns and dashboards.</t>
+  </si>
+  <si>
+    <t>This enhancement improves visual clarity, user engagement, and usability. It eliminates the need for manual image uploads while providing high-quality, scalable visual content for better product identification.</t>
+  </si>
+  <si>
+    <t>Forecasting Integration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,8 +292,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,8 +327,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -158,13 +342,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -740,4 +957,274 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F6663D-199B-475F-BB8E-399E72315137}">
+  <dimension ref="B1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ReportsAndDocuments/presentation Qs.xlsx
+++ b/ReportsAndDocuments/presentation Qs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97794B54-8DEF-40A0-A41B-84BB43D930C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFB8AD9-99D2-4D56-8FF5-7386227AD5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="103">
   <si>
     <t>product category:added</t>
   </si>
@@ -278,13 +278,782 @@
   </si>
   <si>
     <t>Forecasting Integration</t>
+  </si>
+  <si>
+    <t>Technical Implementation / Methods</t>
+  </si>
+  <si>
+    <t>The initially proposed simple logic-based demand estimation and Moving Average algorithm was replaced with a machine learning-based forecasting model using ML.NET Singular Spectrum Analysis (SSA).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML.NET SSA (ForecastBySsa)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with parameters such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>windowSize, seriesLength, trainSize, horizon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Time-series data prepared from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DemandRequest (CreatedAt, QuantityRequested)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> grouped by VendorId &amp; ProductId.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Forecast generation via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/forecasts/generate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Results stored in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DemandForecast table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and consumed by recommendation service. API-driven workflow integrated with React frontend using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fetch/Axios with JWT headers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Built using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>React (Vite)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>REST API integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. State managed via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useState/useEffect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Data fetched from endpoints like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/api/farmer/dashboard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/api/forecasts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Visualization using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chart.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ASP.NET Identity + JWT tokens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Middleware configured with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Issuer, Audience, SigningKey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. React stores token in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>localStorage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and sends via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Authorization: Bearer header</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FarmerRecommendationService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using weighted formula: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Score = f(demand match, distance, relationship score)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. LINQ queries used for aggregation and ranking.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">New entity </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RelationshipStat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with fields like </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TotalRequestedQty, TotalDeliveredQty, RelationshipScore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Calculated using EF Core aggregation queries.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Distance calculated using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Haversine formula</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with fields </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Latitude, Longitude (decimal precision 9,6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Implemented in service layer and returned via API DTOs.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SQL scripts used with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CTE (Common Table Expressions)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DATEADD()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to generate multi-week historical data. Data seeded into </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DemandRequest, InventoryLot, Dispatch tables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>React components</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, controlled inputs, and conditional rendering. Dropdown filtering via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onChange + state filtering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. CSS modules used for styling and layout consistency.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignalR Hub (ChatHub.cs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WebSocket transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Client uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@microsoft/signalr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to establish connection. Messages stored in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ChatMessage table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>This enhancement improves visual clarity, user engagement, and usability. It eliminates the need for manual image uploads while providing high-quality, scalable visual content.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unsplash REST API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Image URLs stored in DTO fields (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ImageUrl, ImageThumbUrl, PhotographerName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Frontend dynamically renders images in product lists and dropdowns.</t>
+    </r>
+  </si>
+  <si>
+    <t>The scoring approach improved interpretability and usability, making recommendation logic easier for non-technical agricultural users to understand and trust by prioritizing demand match,distance and relationship score which calculated score by weighted formula</t>
+  </si>
+  <si>
+    <t>Including relationship history improved recommendation accuracy by accounting for prior collaboration performance and trust which mainly focused on TotalRequestedQty, TotalDeliveredQty, RelationshipScore and finaly calculating relationshipSat using EF Core aggregation queries</t>
+  </si>
+  <si>
+    <t>Geolocation data is required to compute distances between farmers and vendors, which is essential for distance-based ranking and logistics optimization.Here I used Haversine formula with fields Longitude and Latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More realistic historical data was necessary to support reliable machine learning forecasting and to reflect real-world agricultural scenarios.Here I used SQL scripts to generate multi-week historical data.Data seeded into  DemandRequest, InventoryLot, Dispatch tables </t>
+  </si>
+  <si>
+    <t>Real-time messaging was required to support timely coordination, negotiations, and clarification during dispatch and fulfillment processes.Here Implementation use SignalR Hub with WebSocket transport. Client uses @microsoft/signalr to establish connection</t>
+  </si>
+  <si>
+    <t>Image Integration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,6 +1081,11 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -663,24 +1437,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="74.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -688,7 +1462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>1</v>
       </c>
@@ -720,7 +1494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -752,7 +1526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>3</v>
       </c>
@@ -784,7 +1558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>4</v>
       </c>
@@ -816,7 +1590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>5</v>
       </c>
@@ -848,7 +1622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>6</v>
       </c>
@@ -880,7 +1654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>7</v>
       </c>
@@ -912,7 +1686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>8</v>
       </c>
@@ -944,12 +1718,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
@@ -961,16 +1735,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F6663D-199B-475F-BB8E-399E72315137}">
-  <dimension ref="B1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:E40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="34.28515625" customWidth="1"/>
+    <col min="5" max="5" width="103.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:4" ht="41.25" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
@@ -981,7 +1756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
@@ -992,7 +1767,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
@@ -1003,7 +1778,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B5" s="4" t="s">
         <v>39</v>
       </c>
@@ -1014,7 +1789,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B6" s="4" t="s">
         <v>42</v>
       </c>
@@ -1025,7 +1800,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
@@ -1036,7 +1811,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B8" s="4" t="s">
         <v>48</v>
       </c>
@@ -1047,7 +1822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B9" s="4" t="s">
         <v>51</v>
       </c>
@@ -1058,7 +1833,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B10" s="4" t="s">
         <v>54</v>
       </c>
@@ -1069,7 +1844,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B11" s="4" t="s">
         <v>57</v>
       </c>
@@ -1080,7 +1855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" ht="114" customHeight="1" thickBot="1">
       <c r="B12" s="4" t="s">
         <v>60</v>
       </c>
@@ -1091,7 +1866,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
@@ -1102,7 +1877,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" ht="105">
       <c r="B16" s="7" t="s">
         <v>34</v>
       </c>
@@ -1113,7 +1888,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="90">
       <c r="B17" s="7" t="s">
         <v>82</v>
       </c>
@@ -1124,7 +1899,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="90">
       <c r="B18" s="7" t="s">
         <v>39</v>
       </c>
@@ -1135,7 +1910,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="60">
       <c r="B19" s="7" t="s">
         <v>42</v>
       </c>
@@ -1146,7 +1921,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" ht="75">
       <c r="B20" s="7" t="s">
         <v>45</v>
       </c>
@@ -1157,7 +1932,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" ht="60">
       <c r="B21" s="7" t="s">
         <v>48</v>
       </c>
@@ -1168,7 +1943,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" ht="75">
       <c r="B22" s="7" t="s">
         <v>51</v>
       </c>
@@ -1179,7 +1954,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" ht="75">
       <c r="B23" s="7" t="s">
         <v>54</v>
       </c>
@@ -1190,7 +1965,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" ht="75">
       <c r="B24" s="7" t="s">
         <v>57</v>
       </c>
@@ -1201,7 +1976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" ht="60">
       <c r="B25" s="7" t="s">
         <v>60</v>
       </c>
@@ -1212,7 +1987,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" ht="105">
       <c r="B26" s="7" t="s">
         <v>79</v>
       </c>
@@ -1221,6 +1996,174 @@
       </c>
       <c r="D26" s="6" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="105">
+      <c r="B30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="90">
+      <c r="B31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="90">
+      <c r="B32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="60">
+      <c r="B33" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="135">
+      <c r="B34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="135">
+      <c r="B35" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="105">
+      <c r="B36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="135">
+      <c r="B37" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="75">
+      <c r="B38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="135">
+      <c r="B39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="90">
+      <c r="B40" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/presentation Qs.xlsx
+++ b/ReportsAndDocuments/presentation Qs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFB8AD9-99D2-4D56-8FF5-7386227AD5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4485A5D-0AA6-40B1-9804-AF93E96C3094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -981,9 +981,6 @@
     </r>
   </si>
   <si>
-    <t>This enhancement improves visual clarity, user engagement, and usability. It eliminates the need for manual image uploads while providing high-quality, scalable visual content.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Integrated via </t>
     </r>
@@ -1047,6 +1044,9 @@
   </si>
   <si>
     <t>Image Integration</t>
+  </si>
+  <si>
+    <t>This enhancement improves visual clarity, user engagement, and usability. It eliminates the need for manual image uploads while providing high-quality, scalable visual content.Integrated via Unsplash REST API</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1088,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1104,6 +1104,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1135,7 +1141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1155,6 +1161,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1999,13 +2008,13 @@
       </c>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -2076,7 +2085,7 @@
         <v>70</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>89</v>
@@ -2090,7 +2099,7 @@
         <v>72</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>90</v>
@@ -2104,7 +2113,7 @@
         <v>52</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>91</v>
@@ -2118,7 +2127,7 @@
         <v>74</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>92</v>
@@ -2146,24 +2155,24 @@
         <v>77</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="90">
+    <row r="40" spans="2:5" ht="105">
       <c r="B40" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D40" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
